--- a/output/yearly_population_iteration_90_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_90_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4828</v>
+        <v>6394</v>
       </c>
       <c r="C2" t="n">
-        <v>3676</v>
+        <v>6666</v>
       </c>
       <c r="D2" t="n">
-        <v>32193</v>
+        <v>31103</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3102</v>
+        <v>3993</v>
       </c>
       <c r="C3" t="n">
-        <v>4661</v>
+        <v>4946</v>
       </c>
       <c r="D3" t="n">
-        <v>17569</v>
+        <v>17883</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2558</v>
+        <v>3082</v>
       </c>
       <c r="C4" t="n">
-        <v>5013</v>
+        <v>5137</v>
       </c>
       <c r="D4" t="n">
-        <v>7890</v>
+        <v>9339</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1730</v>
+        <v>1852</v>
       </c>
       <c r="C5" t="n">
-        <v>3852</v>
+        <v>3136</v>
       </c>
       <c r="D5" t="n">
-        <v>2590</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>983</v>
+        <v>948</v>
       </c>
       <c r="C6" t="n">
-        <v>2522</v>
+        <v>1806</v>
       </c>
       <c r="D6" t="n">
-        <v>1085</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="C7" t="n">
-        <v>1661</v>
+        <v>1286</v>
       </c>
       <c r="D7" t="n">
-        <v>640</v>
+        <v>675</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C8" t="n">
-        <v>864</v>
+        <v>732</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -940,7 +940,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5595</v>
+        <v>6939</v>
       </c>
       <c r="C2" t="n">
-        <v>12549</v>
+        <v>4117</v>
       </c>
       <c r="D2" t="n">
-        <v>36435</v>
+        <v>38257</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3155</v>
+        <v>4172</v>
       </c>
       <c r="C3" t="n">
-        <v>3692</v>
+        <v>5046</v>
       </c>
       <c r="D3" t="n">
-        <v>18377</v>
+        <v>18479</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2395</v>
+        <v>2978</v>
       </c>
       <c r="C4" t="n">
-        <v>4736</v>
+        <v>4936</v>
       </c>
       <c r="D4" t="n">
-        <v>9154</v>
+        <v>10359</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1852</v>
+        <v>2103</v>
       </c>
       <c r="C5" t="n">
-        <v>4281</v>
+        <v>3981</v>
       </c>
       <c r="D5" t="n">
-        <v>3376</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1202</v>
+        <v>1227</v>
       </c>
       <c r="C6" t="n">
-        <v>3109</v>
+        <v>2400</v>
       </c>
       <c r="D6" t="n">
-        <v>1290</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>607</v>
+        <v>583</v>
       </c>
       <c r="C7" t="n">
-        <v>2032</v>
+        <v>1507</v>
       </c>
       <c r="D7" t="n">
-        <v>703</v>
+        <v>768</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="C8" t="n">
-        <v>1215</v>
+        <v>976</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C9" t="n">
-        <v>587</v>
+        <v>513</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
         <v>209</v>
@@ -1237,7 +1237,7 @@
         <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6713</v>
+        <v>7661</v>
       </c>
       <c r="C2" t="n">
-        <v>9004</v>
+        <v>5561</v>
       </c>
       <c r="D2" t="n">
-        <v>43957</v>
+        <v>42043</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3385</v>
+        <v>4333</v>
       </c>
       <c r="C3" t="n">
-        <v>6531</v>
+        <v>4115</v>
       </c>
       <c r="D3" t="n">
-        <v>19482</v>
+        <v>19798</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2333</v>
+        <v>2959</v>
       </c>
       <c r="C4" t="n">
-        <v>4130</v>
+        <v>4882</v>
       </c>
       <c r="D4" t="n">
-        <v>10292</v>
+        <v>11291</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1850</v>
+        <v>2207</v>
       </c>
       <c r="C5" t="n">
-        <v>4347</v>
+        <v>4272</v>
       </c>
       <c r="D5" t="n">
-        <v>4072</v>
+        <v>4992</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1337</v>
+        <v>1436</v>
       </c>
       <c r="C6" t="n">
-        <v>3575</v>
+        <v>3022</v>
       </c>
       <c r="D6" t="n">
-        <v>1573</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="C7" t="n">
-        <v>2454</v>
+        <v>1882</v>
       </c>
       <c r="D7" t="n">
-        <v>769</v>
+        <v>867</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="C8" t="n">
-        <v>1542</v>
+        <v>1179</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C9" t="n">
-        <v>821</v>
+        <v>694</v>
       </c>
       <c r="D9" t="n">
         <v>333</v>
@@ -1517,7 +1517,7 @@
         <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>398</v>
+        <v>360</v>
       </c>
       <c r="D10" t="n">
         <v>255</v>
@@ -1531,7 +1531,7 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D11" t="n">
         <v>209</v>
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6099</v>
+        <v>7024</v>
       </c>
       <c r="C2" t="n">
-        <v>6050</v>
+        <v>3736</v>
       </c>
       <c r="D2" t="n">
-        <v>35913</v>
+        <v>34058</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4150</v>
+        <v>5326</v>
       </c>
       <c r="C3" t="n">
-        <v>9087</v>
+        <v>6583</v>
       </c>
       <c r="D3" t="n">
-        <v>21017</v>
+        <v>21942</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1709</v>
+        <v>2039</v>
       </c>
       <c r="C4" t="n">
-        <v>6472</v>
+        <v>6866</v>
       </c>
       <c r="D4" t="n">
-        <v>9592</v>
+        <v>10881</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1235</v>
+        <v>1326</v>
       </c>
       <c r="C5" t="n">
-        <v>3503</v>
+        <v>2961</v>
       </c>
       <c r="D5" t="n">
-        <v>2675</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="C6" t="n">
-        <v>2404</v>
+        <v>1844</v>
       </c>
       <c r="D6" t="n">
-        <v>753</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="C7" t="n">
-        <v>1511</v>
+        <v>1155</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>804</v>
+        <v>680</v>
       </c>
       <c r="D8" t="n">
         <v>326</v>
@@ -1814,7 +1814,7 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>390</v>
+        <v>352</v>
       </c>
       <c r="D9" t="n">
         <v>249</v>
@@ -1828,7 +1828,7 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
         <v>204</v>
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3737</v>
+        <v>4327</v>
       </c>
       <c r="C2" t="n">
-        <v>3163</v>
+        <v>1757</v>
       </c>
       <c r="D2" t="n">
-        <v>25342</v>
+        <v>23567</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4298</v>
+        <v>5253</v>
       </c>
       <c r="C3" t="n">
-        <v>6965</v>
+        <v>4777</v>
       </c>
       <c r="D3" t="n">
-        <v>21832</v>
+        <v>22325</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2329</v>
+        <v>2873</v>
       </c>
       <c r="C4" t="n">
-        <v>7816</v>
+        <v>6787</v>
       </c>
       <c r="D4" t="n">
-        <v>11239</v>
+        <v>12458</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1345</v>
+        <v>1505</v>
       </c>
       <c r="C5" t="n">
-        <v>4823</v>
+        <v>4691</v>
       </c>
       <c r="D5" t="n">
-        <v>3508</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C6" t="n">
-        <v>2906</v>
+        <v>2352</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="C7" t="n">
-        <v>1888</v>
+        <v>1434</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>1034</v>
+        <v>867</v>
       </c>
       <c r="D8" t="n">
         <v>340</v>
@@ -2125,7 +2125,7 @@
         <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>446</v>
+        <v>402</v>
       </c>
       <c r="D9" t="n">
         <v>258</v>
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
         <v>212</v>
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3755</v>
+        <v>4041</v>
       </c>
       <c r="C2" t="n">
-        <v>2954</v>
+        <v>2888</v>
       </c>
       <c r="D2" t="n">
-        <v>28294</v>
+        <v>18403</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3409</v>
+        <v>4074</v>
       </c>
       <c r="C3" t="n">
-        <v>4525</v>
+        <v>2946</v>
       </c>
       <c r="D3" t="n">
-        <v>21044</v>
+        <v>20967</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2748</v>
+        <v>3393</v>
       </c>
       <c r="C4" t="n">
-        <v>7303</v>
+        <v>5642</v>
       </c>
       <c r="D4" t="n">
-        <v>12626</v>
+        <v>13784</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1569</v>
+        <v>1855</v>
       </c>
       <c r="C5" t="n">
-        <v>6130</v>
+        <v>5599</v>
       </c>
       <c r="D5" t="n">
-        <v>4555</v>
+        <v>5442</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>966</v>
+        <v>1036</v>
       </c>
       <c r="C6" t="n">
-        <v>3770</v>
+        <v>3429</v>
       </c>
       <c r="D6" t="n">
-        <v>1330</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="C7" t="n">
-        <v>2326</v>
+        <v>1852</v>
       </c>
       <c r="D7" t="n">
-        <v>577</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>1395</v>
+        <v>1108</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -2436,7 +2436,7 @@
         <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>679</v>
+        <v>583</v>
       </c>
       <c r="D9" t="n">
         <v>265</v>
@@ -2450,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
         <v>216</v>
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
         <v>24</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2234</v>
+        <v>2398</v>
       </c>
       <c r="C2" t="n">
-        <v>1361</v>
+        <v>1329</v>
       </c>
       <c r="D2" t="n">
-        <v>19502</v>
+        <v>12693</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3369</v>
+        <v>3920</v>
       </c>
       <c r="C3" t="n">
-        <v>3839</v>
+        <v>2826</v>
       </c>
       <c r="D3" t="n">
-        <v>21350</v>
+        <v>20176</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3037</v>
+        <v>3737</v>
       </c>
       <c r="C4" t="n">
-        <v>6988</v>
+        <v>5134</v>
       </c>
       <c r="D4" t="n">
-        <v>13821</v>
+        <v>14716</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1659</v>
+        <v>1914</v>
       </c>
       <c r="C5" t="n">
-        <v>7258</v>
+        <v>6433</v>
       </c>
       <c r="D5" t="n">
-        <v>4836</v>
+        <v>5907</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>811</v>
+        <v>840</v>
       </c>
       <c r="C6" t="n">
-        <v>4592</v>
+        <v>4164</v>
       </c>
       <c r="D6" t="n">
-        <v>1301</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>2479</v>
+        <v>1979</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1102</v>
+        <v>929</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
         <v>23</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3361</v>
+        <v>3761</v>
       </c>
       <c r="C2" t="n">
-        <v>5347</v>
+        <v>2826</v>
       </c>
       <c r="D2" t="n">
-        <v>20400</v>
+        <v>14870</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2454</v>
+        <v>2809</v>
       </c>
       <c r="C3" t="n">
-        <v>2398</v>
+        <v>1882</v>
       </c>
       <c r="D3" t="n">
-        <v>19663</v>
+        <v>17802</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2804</v>
+        <v>3341</v>
       </c>
       <c r="C4" t="n">
-        <v>5398</v>
+        <v>3946</v>
       </c>
       <c r="D4" t="n">
-        <v>14629</v>
+        <v>15159</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1973</v>
+        <v>2362</v>
       </c>
       <c r="C5" t="n">
-        <v>7054</v>
+        <v>5762</v>
       </c>
       <c r="D5" t="n">
-        <v>6115</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1037</v>
+        <v>1142</v>
       </c>
       <c r="C6" t="n">
-        <v>5720</v>
+        <v>5145</v>
       </c>
       <c r="D6" t="n">
-        <v>1759</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C7" t="n">
-        <v>3375</v>
+        <v>2916</v>
       </c>
       <c r="D7" t="n">
-        <v>669</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1622</v>
+        <v>1337</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>569</v>
+        <v>509</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2236</v>
+        <v>2615</v>
       </c>
       <c r="C2" t="n">
-        <v>3989</v>
+        <v>2950</v>
       </c>
       <c r="D2" t="n">
-        <v>14568</v>
+        <v>11716</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2410</v>
+        <v>2740</v>
       </c>
       <c r="C3" t="n">
-        <v>3237</v>
+        <v>2074</v>
       </c>
       <c r="D3" t="n">
-        <v>18681</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2487</v>
+        <v>2929</v>
       </c>
       <c r="C4" t="n">
-        <v>4202</v>
+        <v>3105</v>
       </c>
       <c r="D4" t="n">
-        <v>15001</v>
+        <v>15198</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2135</v>
+        <v>2560</v>
       </c>
       <c r="C5" t="n">
-        <v>6574</v>
+        <v>5128</v>
       </c>
       <c r="D5" t="n">
-        <v>7027</v>
+        <v>7931</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1208</v>
+        <v>1360</v>
       </c>
       <c r="C6" t="n">
-        <v>6371</v>
+        <v>5561</v>
       </c>
       <c r="D6" t="n">
-        <v>2148</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>4179</v>
+        <v>3704</v>
       </c>
       <c r="D7" t="n">
-        <v>764</v>
+        <v>825</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>2061</v>
+        <v>1760</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>661</v>
+        <v>605</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3428,7 +3428,7 @@
         <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3239</v>
+        <v>3935</v>
       </c>
       <c r="C2" t="n">
-        <v>8985</v>
+        <v>4169</v>
       </c>
       <c r="D2" t="n">
-        <v>20248</v>
+        <v>13125</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1975</v>
+        <v>2263</v>
       </c>
       <c r="C3" t="n">
-        <v>3145</v>
+        <v>2184</v>
       </c>
       <c r="D3" t="n">
-        <v>16991</v>
+        <v>14885</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2137</v>
+        <v>2509</v>
       </c>
       <c r="C4" t="n">
-        <v>3697</v>
+        <v>2585</v>
       </c>
       <c r="D4" t="n">
-        <v>15074</v>
+        <v>14951</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2061</v>
+        <v>2458</v>
       </c>
       <c r="C5" t="n">
-        <v>5458</v>
+        <v>4166</v>
       </c>
       <c r="D5" t="n">
-        <v>7817</v>
+        <v>8736</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1423</v>
+        <v>1660</v>
       </c>
       <c r="C6" t="n">
-        <v>6396</v>
+        <v>5337</v>
       </c>
       <c r="D6" t="n">
-        <v>2775</v>
+        <v>3275</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>517</v>
+        <v>584</v>
       </c>
       <c r="C7" t="n">
-        <v>5056</v>
+        <v>4430</v>
       </c>
       <c r="D7" t="n">
-        <v>932</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>2807</v>
+        <v>2500</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1133</v>
+        <v>1006</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4766</v>
+        <v>4407</v>
       </c>
       <c r="C2" t="n">
-        <v>7939</v>
+        <v>6572</v>
       </c>
       <c r="D2" t="n">
-        <v>6612</v>
+        <v>13735</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2317</v>
+        <v>2754</v>
       </c>
       <c r="C2" t="n">
-        <v>5103</v>
+        <v>2302</v>
       </c>
       <c r="D2" t="n">
-        <v>14902</v>
+        <v>9661</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2641</v>
+        <v>3106</v>
       </c>
       <c r="C3" t="n">
-        <v>4771</v>
+        <v>2857</v>
       </c>
       <c r="D3" t="n">
-        <v>18620</v>
+        <v>15990</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2994</v>
+        <v>3525</v>
       </c>
       <c r="C4" t="n">
-        <v>5557</v>
+        <v>3953</v>
       </c>
       <c r="D4" t="n">
-        <v>15259</v>
+        <v>15504</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1371</v>
+        <v>1647</v>
       </c>
       <c r="C5" t="n">
-        <v>8577</v>
+        <v>6879</v>
       </c>
       <c r="D5" t="n">
-        <v>7063</v>
+        <v>7946</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>477</v>
+        <v>539</v>
       </c>
       <c r="C6" t="n">
-        <v>6208</v>
+        <v>5492</v>
       </c>
       <c r="D6" t="n">
-        <v>2154</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>2750</v>
+        <v>2450</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1110</v>
+        <v>985</v>
       </c>
       <c r="D8" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6337</v>
+        <v>5998</v>
       </c>
       <c r="C2" t="n">
-        <v>4860</v>
+        <v>4245</v>
       </c>
       <c r="D2" t="n">
-        <v>12074</v>
+        <v>18481</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2026</v>
+        <v>1874</v>
       </c>
       <c r="C3" t="n">
-        <v>4001</v>
+        <v>3312</v>
       </c>
       <c r="D3" t="n">
-        <v>1750</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4375</v>
+        <v>4004</v>
       </c>
       <c r="C2" t="n">
-        <v>4400</v>
+        <v>2370</v>
       </c>
       <c r="D2" t="n">
-        <v>14129</v>
+        <v>24760</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3431</v>
+        <v>3229</v>
       </c>
       <c r="C3" t="n">
-        <v>3870</v>
+        <v>3311</v>
       </c>
       <c r="D3" t="n">
-        <v>3355</v>
+        <v>5339</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>913</v>
+        <v>847</v>
       </c>
       <c r="C4" t="n">
-        <v>2425</v>
+        <v>1984</v>
       </c>
       <c r="D4" t="n">
-        <v>1533</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5369</v>
+        <v>5741</v>
       </c>
       <c r="C2" t="n">
-        <v>5156</v>
+        <v>3876</v>
       </c>
       <c r="D2" t="n">
-        <v>25298</v>
+        <v>31675</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3205</v>
+        <v>2972</v>
       </c>
       <c r="C3" t="n">
-        <v>3600</v>
+        <v>2421</v>
       </c>
       <c r="D3" t="n">
-        <v>4837</v>
+        <v>8061</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1836</v>
+        <v>1723</v>
       </c>
       <c r="C4" t="n">
-        <v>3193</v>
+        <v>2694</v>
       </c>
       <c r="D4" t="n">
-        <v>1836</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="C5" t="n">
-        <v>1419</v>
+        <v>1181</v>
       </c>
       <c r="D5" t="n">
-        <v>1201</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5820</v>
+        <v>5471</v>
       </c>
       <c r="C2" t="n">
-        <v>5344</v>
+        <v>3018</v>
       </c>
       <c r="D2" t="n">
-        <v>31313</v>
+        <v>43103</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3465</v>
+        <v>3500</v>
       </c>
       <c r="C3" t="n">
-        <v>3871</v>
+        <v>2759</v>
       </c>
       <c r="D3" t="n">
-        <v>7606</v>
+        <v>11082</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2128</v>
+        <v>1997</v>
       </c>
       <c r="C4" t="n">
-        <v>3314</v>
+        <v>2465</v>
       </c>
       <c r="D4" t="n">
-        <v>2309</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>944</v>
+        <v>872</v>
       </c>
       <c r="C5" t="n">
-        <v>2326</v>
+        <v>1955</v>
       </c>
       <c r="D5" t="n">
-        <v>1280</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="C6" t="n">
-        <v>867</v>
+        <v>745</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>216</v>
@@ -5605,7 +5605,7 @@
         <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5511</v>
+        <v>7496</v>
       </c>
       <c r="C2" t="n">
-        <v>9447</v>
+        <v>9713</v>
       </c>
       <c r="D2" t="n">
-        <v>43538</v>
+        <v>34167</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3368</v>
+        <v>3282</v>
       </c>
       <c r="C3" t="n">
-        <v>3830</v>
+        <v>2368</v>
       </c>
       <c r="D3" t="n">
-        <v>10041</v>
+        <v>14269</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1747</v>
+        <v>1692</v>
       </c>
       <c r="C4" t="n">
-        <v>2941</v>
+        <v>2133</v>
       </c>
       <c r="D4" t="n">
-        <v>2778</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>746</v>
       </c>
       <c r="C5" t="n">
-        <v>2079</v>
+        <v>1622</v>
       </c>
       <c r="D5" t="n">
-        <v>1158</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="C6" t="n">
-        <v>1074</v>
+        <v>908</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>789</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>389</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
         <v>513</v>
@@ -5846,7 +5846,7 @@
         <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>194</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5916,7 +5916,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4605</v>
+        <v>6284</v>
       </c>
       <c r="C2" t="n">
-        <v>6162</v>
+        <v>8263</v>
       </c>
       <c r="D2" t="n">
-        <v>31333</v>
+        <v>27655</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3685</v>
+        <v>4492</v>
       </c>
       <c r="C3" t="n">
-        <v>6160</v>
+        <v>5791</v>
       </c>
       <c r="D3" t="n">
-        <v>15181</v>
+        <v>16698</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2250</v>
+        <v>2173</v>
       </c>
       <c r="C4" t="n">
-        <v>3426</v>
+        <v>2233</v>
       </c>
       <c r="D4" t="n">
-        <v>4227</v>
+        <v>6071</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1128</v>
+        <v>1094</v>
       </c>
       <c r="C5" t="n">
-        <v>2548</v>
+        <v>1892</v>
       </c>
       <c r="D5" t="n">
-        <v>1449</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>507</v>
+        <v>472</v>
       </c>
       <c r="C6" t="n">
-        <v>1639</v>
+        <v>1308</v>
       </c>
       <c r="D6" t="n">
-        <v>820</v>
+        <v>887</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>778</v>
+        <v>667</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6227,7 +6227,7 @@
         <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4125</v>
+        <v>5317</v>
       </c>
       <c r="C2" t="n">
-        <v>5359</v>
+        <v>5166</v>
       </c>
       <c r="D2" t="n">
-        <v>30298</v>
+        <v>29419</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3443</v>
+        <v>4427</v>
       </c>
       <c r="C3" t="n">
-        <v>5333</v>
+        <v>6189</v>
       </c>
       <c r="D3" t="n">
-        <v>16672</v>
+        <v>17248</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2535</v>
+        <v>2876</v>
       </c>
       <c r="C4" t="n">
-        <v>4870</v>
+        <v>4235</v>
       </c>
       <c r="D4" t="n">
-        <v>6161</v>
+        <v>7868</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1482</v>
+        <v>1424</v>
       </c>
       <c r="C5" t="n">
-        <v>2983</v>
+        <v>2042</v>
       </c>
       <c r="D5" t="n">
-        <v>1938</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>737</v>
+        <v>714</v>
       </c>
       <c r="C6" t="n">
-        <v>2108</v>
+        <v>1606</v>
       </c>
       <c r="D6" t="n">
-        <v>923</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="C7" t="n">
-        <v>1233</v>
+        <v>999</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>547</v>
+        <v>487</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">

--- a/output/yearly_population_iteration_90_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_90_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6394</v>
+        <v>6261</v>
       </c>
       <c r="C2" t="n">
-        <v>6666</v>
+        <v>9461</v>
       </c>
       <c r="D2" t="n">
-        <v>31103</v>
+        <v>38577</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3993</v>
+        <v>3430</v>
       </c>
       <c r="C3" t="n">
-        <v>4946</v>
+        <v>7009</v>
       </c>
       <c r="D3" t="n">
-        <v>17883</v>
+        <v>16376</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3082</v>
+        <v>2462</v>
       </c>
       <c r="C4" t="n">
-        <v>5137</v>
+        <v>5801</v>
       </c>
       <c r="D4" t="n">
-        <v>9339</v>
+        <v>6746</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1852</v>
+        <v>1692</v>
       </c>
       <c r="C5" t="n">
-        <v>3136</v>
+        <v>4236</v>
       </c>
       <c r="D5" t="n">
-        <v>3431</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>948</v>
+        <v>996</v>
       </c>
       <c r="C6" t="n">
-        <v>1806</v>
+        <v>2956</v>
       </c>
       <c r="D6" t="n">
-        <v>1313</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>431</v>
+        <v>472</v>
       </c>
       <c r="C7" t="n">
-        <v>1286</v>
+        <v>1867</v>
       </c>
       <c r="D7" t="n">
-        <v>675</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="C8" t="n">
-        <v>732</v>
+        <v>885</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -898,7 +898,7 @@
         <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6939</v>
+        <v>5754</v>
       </c>
       <c r="C2" t="n">
-        <v>4117</v>
+        <v>11047</v>
       </c>
       <c r="D2" t="n">
-        <v>38257</v>
+        <v>46678</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4172</v>
+        <v>3827</v>
       </c>
       <c r="C3" t="n">
-        <v>5046</v>
+        <v>7148</v>
       </c>
       <c r="D3" t="n">
-        <v>18479</v>
+        <v>18294</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2978</v>
+        <v>2456</v>
       </c>
       <c r="C4" t="n">
-        <v>4936</v>
+        <v>6260</v>
       </c>
       <c r="D4" t="n">
-        <v>10359</v>
+        <v>8112</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2103</v>
+        <v>1792</v>
       </c>
       <c r="C5" t="n">
-        <v>3981</v>
+        <v>4828</v>
       </c>
       <c r="D5" t="n">
-        <v>4290</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1227</v>
+        <v>1180</v>
       </c>
       <c r="C6" t="n">
-        <v>2400</v>
+        <v>3504</v>
       </c>
       <c r="D6" t="n">
-        <v>1607</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>583</v>
+        <v>628</v>
       </c>
       <c r="C7" t="n">
-        <v>1507</v>
+        <v>2328</v>
       </c>
       <c r="D7" t="n">
-        <v>768</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="C8" t="n">
-        <v>976</v>
+        <v>1308</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>513</v>
+        <v>577</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7661</v>
+        <v>6287</v>
       </c>
       <c r="C2" t="n">
-        <v>5561</v>
+        <v>16380</v>
       </c>
       <c r="D2" t="n">
-        <v>42043</v>
+        <v>38403</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4333</v>
+        <v>3803</v>
       </c>
       <c r="C3" t="n">
-        <v>4115</v>
+        <v>7751</v>
       </c>
       <c r="D3" t="n">
-        <v>19798</v>
+        <v>20529</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2959</v>
+        <v>2545</v>
       </c>
       <c r="C4" t="n">
-        <v>4882</v>
+        <v>6453</v>
       </c>
       <c r="D4" t="n">
-        <v>11291</v>
+        <v>9253</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2207</v>
+        <v>1829</v>
       </c>
       <c r="C5" t="n">
-        <v>4272</v>
+        <v>5332</v>
       </c>
       <c r="D5" t="n">
-        <v>4992</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1436</v>
+        <v>1299</v>
       </c>
       <c r="C6" t="n">
-        <v>3022</v>
+        <v>3972</v>
       </c>
       <c r="D6" t="n">
-        <v>1972</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="C7" t="n">
-        <v>1882</v>
+        <v>2776</v>
       </c>
       <c r="D7" t="n">
-        <v>867</v>
+        <v>768</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="C8" t="n">
-        <v>1179</v>
+        <v>1707</v>
       </c>
       <c r="D8" t="n">
-        <v>497</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C9" t="n">
-        <v>694</v>
+        <v>843</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
         <v>103</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1618,7 +1618,7 @@
         <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7024</v>
+        <v>5880</v>
       </c>
       <c r="C2" t="n">
-        <v>3736</v>
+        <v>11269</v>
       </c>
       <c r="D2" t="n">
-        <v>34058</v>
+        <v>31707</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5326</v>
+        <v>4566</v>
       </c>
       <c r="C3" t="n">
-        <v>6583</v>
+        <v>11939</v>
       </c>
       <c r="D3" t="n">
-        <v>21942</v>
+        <v>21564</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2039</v>
+        <v>1689</v>
       </c>
       <c r="C4" t="n">
-        <v>6866</v>
+        <v>8649</v>
       </c>
       <c r="D4" t="n">
-        <v>10881</v>
+        <v>8568</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1326</v>
+        <v>1200</v>
       </c>
       <c r="C5" t="n">
-        <v>2961</v>
+        <v>3892</v>
       </c>
       <c r="D5" t="n">
-        <v>3322</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="C6" t="n">
-        <v>1844</v>
+        <v>2720</v>
       </c>
       <c r="D6" t="n">
-        <v>849</v>
+        <v>752</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C7" t="n">
-        <v>1155</v>
+        <v>1672</v>
       </c>
       <c r="D7" t="n">
-        <v>487</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>680</v>
+        <v>826</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
@@ -1915,7 +1915,7 @@
         <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4327</v>
+        <v>3642</v>
       </c>
       <c r="C2" t="n">
-        <v>1757</v>
+        <v>5277</v>
       </c>
       <c r="D2" t="n">
-        <v>23567</v>
+        <v>22657</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5253</v>
+        <v>4449</v>
       </c>
       <c r="C3" t="n">
-        <v>4777</v>
+        <v>10557</v>
       </c>
       <c r="D3" t="n">
-        <v>22325</v>
+        <v>21908</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2873</v>
+        <v>2416</v>
       </c>
       <c r="C4" t="n">
-        <v>6787</v>
+        <v>10317</v>
       </c>
       <c r="D4" t="n">
-        <v>12458</v>
+        <v>10261</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1505</v>
+        <v>1310</v>
       </c>
       <c r="C5" t="n">
-        <v>4691</v>
+        <v>5915</v>
       </c>
       <c r="D5" t="n">
-        <v>4228</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>843</v>
+        <v>828</v>
       </c>
       <c r="C6" t="n">
-        <v>2352</v>
+        <v>3253</v>
       </c>
       <c r="D6" t="n">
-        <v>1101</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>1434</v>
+        <v>2096</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>867</v>
+        <v>1076</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
+        <v>164</v>
+      </c>
+      <c r="D11" t="n">
         <v>167</v>
-      </c>
-      <c r="D11" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2212,7 +2212,7 @@
         <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4041</v>
+        <v>3287</v>
       </c>
       <c r="C2" t="n">
-        <v>2888</v>
+        <v>3840</v>
       </c>
       <c r="D2" t="n">
-        <v>18403</v>
+        <v>21913</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4074</v>
+        <v>3460</v>
       </c>
       <c r="C3" t="n">
-        <v>2946</v>
+        <v>7220</v>
       </c>
       <c r="D3" t="n">
-        <v>20967</v>
+        <v>20537</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3393</v>
+        <v>2830</v>
       </c>
       <c r="C4" t="n">
-        <v>5642</v>
+        <v>10217</v>
       </c>
       <c r="D4" t="n">
-        <v>13784</v>
+        <v>11849</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1855</v>
+        <v>1568</v>
       </c>
       <c r="C5" t="n">
-        <v>5599</v>
+        <v>7820</v>
       </c>
       <c r="D5" t="n">
-        <v>5442</v>
+        <v>4162</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1036</v>
+        <v>943</v>
       </c>
       <c r="C6" t="n">
-        <v>3429</v>
+        <v>4429</v>
       </c>
       <c r="D6" t="n">
-        <v>1566</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C7" t="n">
-        <v>1852</v>
+        <v>2603</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>1108</v>
+        <v>1485</v>
       </c>
       <c r="D8" t="n">
-        <v>366</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>583</v>
+        <v>662</v>
       </c>
       <c r="D9" t="n">
         <v>265</v>
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2398</v>
+        <v>1984</v>
       </c>
       <c r="C2" t="n">
-        <v>1329</v>
+        <v>1862</v>
       </c>
       <c r="D2" t="n">
-        <v>12693</v>
+        <v>15323</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3920</v>
+        <v>3300</v>
       </c>
       <c r="C3" t="n">
-        <v>2826</v>
+        <v>5903</v>
       </c>
       <c r="D3" t="n">
-        <v>20176</v>
+        <v>20220</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3737</v>
+        <v>3098</v>
       </c>
       <c r="C4" t="n">
-        <v>5134</v>
+        <v>10035</v>
       </c>
       <c r="D4" t="n">
-        <v>14716</v>
+        <v>12848</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1914</v>
+        <v>1641</v>
       </c>
       <c r="C5" t="n">
-        <v>6433</v>
+        <v>9570</v>
       </c>
       <c r="D5" t="n">
-        <v>5907</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>840</v>
+        <v>789</v>
       </c>
       <c r="C6" t="n">
-        <v>4164</v>
+        <v>5178</v>
       </c>
       <c r="D6" t="n">
-        <v>1525</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>1979</v>
+        <v>2727</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>929</v>
+        <v>1085</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3761</v>
+        <v>3073</v>
       </c>
       <c r="C2" t="n">
-        <v>2826</v>
+        <v>9798</v>
       </c>
       <c r="D2" t="n">
-        <v>14870</v>
+        <v>14062</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2809</v>
+        <v>2378</v>
       </c>
       <c r="C3" t="n">
-        <v>1882</v>
+        <v>3676</v>
       </c>
       <c r="D3" t="n">
-        <v>17802</v>
+        <v>18266</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3341</v>
+        <v>2784</v>
       </c>
       <c r="C4" t="n">
-        <v>3946</v>
+        <v>8018</v>
       </c>
       <c r="D4" t="n">
-        <v>15159</v>
+        <v>13589</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2362</v>
+        <v>1970</v>
       </c>
       <c r="C5" t="n">
-        <v>5762</v>
+        <v>9663</v>
       </c>
       <c r="D5" t="n">
-        <v>7080</v>
+        <v>5507</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1142</v>
+        <v>1009</v>
       </c>
       <c r="C6" t="n">
-        <v>5145</v>
+        <v>6954</v>
       </c>
       <c r="D6" t="n">
-        <v>2150</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="C7" t="n">
-        <v>2916</v>
+        <v>3689</v>
       </c>
       <c r="D7" t="n">
-        <v>720</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>1337</v>
+        <v>1685</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2615</v>
+        <v>2178</v>
       </c>
       <c r="C2" t="n">
-        <v>2950</v>
+        <v>4809</v>
       </c>
       <c r="D2" t="n">
-        <v>11716</v>
+        <v>11322</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2740</v>
+        <v>2274</v>
       </c>
       <c r="C3" t="n">
-        <v>2074</v>
+        <v>5452</v>
       </c>
       <c r="D3" t="n">
-        <v>16600</v>
+        <v>16830</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2929</v>
+        <v>2461</v>
       </c>
       <c r="C4" t="n">
-        <v>3105</v>
+        <v>6373</v>
       </c>
       <c r="D4" t="n">
-        <v>15198</v>
+        <v>13890</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2560</v>
+        <v>2099</v>
       </c>
       <c r="C5" t="n">
-        <v>5128</v>
+        <v>9264</v>
       </c>
       <c r="D5" t="n">
-        <v>7931</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1360</v>
+        <v>1175</v>
       </c>
       <c r="C6" t="n">
-        <v>5561</v>
+        <v>8030</v>
       </c>
       <c r="D6" t="n">
-        <v>2592</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="C7" t="n">
-        <v>3704</v>
+        <v>4676</v>
       </c>
       <c r="D7" t="n">
-        <v>825</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1760</v>
+        <v>2140</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3935</v>
+        <v>3583</v>
       </c>
       <c r="C2" t="n">
-        <v>4169</v>
+        <v>10522</v>
       </c>
       <c r="D2" t="n">
-        <v>13125</v>
+        <v>14729</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2263</v>
+        <v>1888</v>
       </c>
       <c r="C3" t="n">
-        <v>2184</v>
+        <v>4689</v>
       </c>
       <c r="D3" t="n">
-        <v>14885</v>
+        <v>15253</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2509</v>
+        <v>2084</v>
       </c>
       <c r="C4" t="n">
-        <v>2585</v>
+        <v>5807</v>
       </c>
       <c r="D4" t="n">
-        <v>14951</v>
+        <v>13729</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2458</v>
+        <v>2028</v>
       </c>
       <c r="C5" t="n">
-        <v>4166</v>
+        <v>7933</v>
       </c>
       <c r="D5" t="n">
-        <v>8736</v>
+        <v>7126</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1660</v>
+        <v>1374</v>
       </c>
       <c r="C6" t="n">
-        <v>5337</v>
+        <v>8504</v>
       </c>
       <c r="D6" t="n">
-        <v>3275</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>584</v>
+        <v>479</v>
       </c>
       <c r="C7" t="n">
-        <v>4430</v>
+        <v>5857</v>
       </c>
       <c r="D7" t="n">
-        <v>1041</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>2500</v>
+        <v>2984</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1006</v>
+        <v>1089</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4407</v>
+        <v>5311</v>
       </c>
       <c r="C2" t="n">
-        <v>6572</v>
+        <v>6522</v>
       </c>
       <c r="D2" t="n">
-        <v>13735</v>
+        <v>7655</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2754</v>
+        <v>2617</v>
       </c>
       <c r="C2" t="n">
-        <v>2302</v>
+        <v>6144</v>
       </c>
       <c r="D2" t="n">
-        <v>9661</v>
+        <v>10958</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3106</v>
+        <v>2559</v>
       </c>
       <c r="C3" t="n">
-        <v>2857</v>
+        <v>6424</v>
       </c>
       <c r="D3" t="n">
-        <v>15990</v>
+        <v>16522</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3525</v>
+        <v>2938</v>
       </c>
       <c r="C4" t="n">
-        <v>3953</v>
+        <v>8513</v>
       </c>
       <c r="D4" t="n">
-        <v>15504</v>
+        <v>13835</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1647</v>
+        <v>1288</v>
       </c>
       <c r="C5" t="n">
-        <v>6879</v>
+        <v>11860</v>
       </c>
       <c r="D5" t="n">
-        <v>7946</v>
+        <v>6365</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>539</v>
+        <v>442</v>
       </c>
       <c r="C6" t="n">
-        <v>5492</v>
+        <v>7239</v>
       </c>
       <c r="D6" t="n">
-        <v>2514</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>2450</v>
+        <v>2924</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>985</v>
+        <v>1067</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5998</v>
+        <v>6970</v>
       </c>
       <c r="C2" t="n">
-        <v>4245</v>
+        <v>6991</v>
       </c>
       <c r="D2" t="n">
-        <v>18481</v>
+        <v>12361</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1874</v>
+        <v>2257</v>
       </c>
       <c r="C3" t="n">
-        <v>3312</v>
+        <v>3287</v>
       </c>
       <c r="D3" t="n">
-        <v>2946</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4004</v>
+        <v>4543</v>
       </c>
       <c r="C2" t="n">
-        <v>2370</v>
+        <v>6003</v>
       </c>
       <c r="D2" t="n">
-        <v>24760</v>
+        <v>19202</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3229</v>
+        <v>3786</v>
       </c>
       <c r="C3" t="n">
-        <v>3311</v>
+        <v>4698</v>
       </c>
       <c r="D3" t="n">
-        <v>5339</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>847</v>
+        <v>1014</v>
       </c>
       <c r="C4" t="n">
-        <v>1984</v>
+        <v>1968</v>
       </c>
       <c r="D4" t="n">
-        <v>1775</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5741</v>
+        <v>4861</v>
       </c>
       <c r="C2" t="n">
-        <v>3876</v>
+        <v>6461</v>
       </c>
       <c r="D2" t="n">
-        <v>31675</v>
+        <v>20174</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2972</v>
+        <v>3425</v>
       </c>
       <c r="C3" t="n">
-        <v>2421</v>
+        <v>4682</v>
       </c>
       <c r="D3" t="n">
-        <v>8061</v>
+        <v>5787</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1723</v>
+        <v>2029</v>
       </c>
       <c r="C4" t="n">
-        <v>2694</v>
+        <v>3473</v>
       </c>
       <c r="D4" t="n">
-        <v>2405</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>409</v>
+        <v>477</v>
       </c>
       <c r="C5" t="n">
-        <v>1181</v>
+        <v>1169</v>
       </c>
       <c r="D5" t="n">
-        <v>1245</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5471</v>
+        <v>5011</v>
       </c>
       <c r="C2" t="n">
-        <v>3018</v>
+        <v>6328</v>
       </c>
       <c r="D2" t="n">
-        <v>43103</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3500</v>
+        <v>3374</v>
       </c>
       <c r="C3" t="n">
-        <v>2759</v>
+        <v>4872</v>
       </c>
       <c r="D3" t="n">
-        <v>11082</v>
+        <v>7566</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1997</v>
+        <v>2322</v>
       </c>
       <c r="C4" t="n">
-        <v>2465</v>
+        <v>4017</v>
       </c>
       <c r="D4" t="n">
-        <v>3340</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>872</v>
+        <v>1024</v>
       </c>
       <c r="C5" t="n">
-        <v>1955</v>
+        <v>2361</v>
       </c>
       <c r="D5" t="n">
-        <v>1418</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="D6" t="n">
-        <v>959</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,7 +5574,7 @@
         <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
         <v>216</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>178</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7496</v>
+        <v>5830</v>
       </c>
       <c r="C2" t="n">
-        <v>9713</v>
+        <v>8300</v>
       </c>
       <c r="D2" t="n">
-        <v>34167</v>
+        <v>29911</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3282</v>
+        <v>3071</v>
       </c>
       <c r="C3" t="n">
-        <v>2368</v>
+        <v>4600</v>
       </c>
       <c r="D3" t="n">
-        <v>14269</v>
+        <v>8632</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1692</v>
+        <v>1756</v>
       </c>
       <c r="C4" t="n">
-        <v>2133</v>
+        <v>3646</v>
       </c>
       <c r="D4" t="n">
-        <v>4032</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>746</v>
+        <v>871</v>
       </c>
       <c r="C5" t="n">
-        <v>1622</v>
+        <v>2365</v>
       </c>
       <c r="D5" t="n">
-        <v>1399</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>266</v>
+        <v>309</v>
       </c>
       <c r="C6" t="n">
-        <v>908</v>
+        <v>1044</v>
       </c>
       <c r="D6" t="n">
-        <v>789</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D7" t="n">
         <v>513</v>
@@ -5846,7 +5846,7 @@
         <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6284</v>
+        <v>4402</v>
       </c>
       <c r="C2" t="n">
-        <v>8263</v>
+        <v>9583</v>
       </c>
       <c r="D2" t="n">
-        <v>27655</v>
+        <v>34232</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4492</v>
+        <v>3701</v>
       </c>
       <c r="C3" t="n">
-        <v>5791</v>
+        <v>5839</v>
       </c>
       <c r="D3" t="n">
-        <v>16698</v>
+        <v>11727</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2173</v>
+        <v>2119</v>
       </c>
       <c r="C4" t="n">
-        <v>2233</v>
+        <v>4156</v>
       </c>
       <c r="D4" t="n">
-        <v>6071</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1094</v>
+        <v>1165</v>
       </c>
       <c r="C5" t="n">
-        <v>1892</v>
+        <v>3078</v>
       </c>
       <c r="D5" t="n">
-        <v>1887</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>472</v>
+        <v>550</v>
       </c>
       <c r="C6" t="n">
-        <v>1308</v>
+        <v>1791</v>
       </c>
       <c r="D6" t="n">
-        <v>887</v>
+        <v>831</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>667</v>
+        <v>743</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5317</v>
+        <v>5191</v>
       </c>
       <c r="C2" t="n">
-        <v>5166</v>
+        <v>9084</v>
       </c>
       <c r="D2" t="n">
-        <v>29419</v>
+        <v>34549</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4427</v>
+        <v>3333</v>
       </c>
       <c r="C3" t="n">
-        <v>6189</v>
+        <v>6821</v>
       </c>
       <c r="D3" t="n">
-        <v>17248</v>
+        <v>14483</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2876</v>
+        <v>2483</v>
       </c>
       <c r="C4" t="n">
-        <v>4235</v>
+        <v>5022</v>
       </c>
       <c r="D4" t="n">
-        <v>7868</v>
+        <v>5391</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1424</v>
+        <v>1447</v>
       </c>
       <c r="C5" t="n">
-        <v>2042</v>
+        <v>3574</v>
       </c>
       <c r="D5" t="n">
-        <v>2632</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>714</v>
+        <v>774</v>
       </c>
       <c r="C6" t="n">
-        <v>1606</v>
+        <v>2462</v>
       </c>
       <c r="D6" t="n">
-        <v>1056</v>
+        <v>943</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>999</v>
+        <v>1297</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>487</v>
+        <v>521</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">

--- a/output/yearly_population_iteration_90_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_90_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6261</v>
+        <v>986</v>
       </c>
       <c r="C2" t="n">
-        <v>9461</v>
+        <v>2467</v>
       </c>
       <c r="D2" t="n">
-        <v>38577</v>
+        <v>17462</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3430</v>
+        <v>1774</v>
       </c>
       <c r="C3" t="n">
-        <v>7009</v>
+        <v>6414</v>
       </c>
       <c r="D3" t="n">
-        <v>16376</v>
+        <v>16252</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2462</v>
+        <v>1129</v>
       </c>
       <c r="C4" t="n">
-        <v>5801</v>
+        <v>6338</v>
       </c>
       <c r="D4" t="n">
-        <v>6746</v>
+        <v>6908</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1692</v>
+        <v>478</v>
       </c>
       <c r="C5" t="n">
-        <v>4236</v>
+        <v>3040</v>
       </c>
       <c r="D5" t="n">
-        <v>2455</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>996</v>
+        <v>218</v>
       </c>
       <c r="C6" t="n">
-        <v>2956</v>
+        <v>1124</v>
       </c>
       <c r="D6" t="n">
-        <v>1079</v>
+        <v>770</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>472</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>1867</v>
+        <v>482</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>181</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>885</v>
+        <v>331</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>53</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>143</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5754</v>
+        <v>1514</v>
       </c>
       <c r="C2" t="n">
-        <v>11047</v>
+        <v>7332</v>
       </c>
       <c r="D2" t="n">
-        <v>46678</v>
+        <v>17055</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3827</v>
+        <v>1172</v>
       </c>
       <c r="C3" t="n">
-        <v>7148</v>
+        <v>3708</v>
       </c>
       <c r="D3" t="n">
-        <v>18294</v>
+        <v>15275</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2456</v>
+        <v>1254</v>
       </c>
       <c r="C4" t="n">
-        <v>6260</v>
+        <v>6310</v>
       </c>
       <c r="D4" t="n">
-        <v>8112</v>
+        <v>8492</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1792</v>
+        <v>689</v>
       </c>
       <c r="C5" t="n">
-        <v>4828</v>
+        <v>4749</v>
       </c>
       <c r="D5" t="n">
-        <v>3015</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1180</v>
+        <v>310</v>
       </c>
       <c r="C6" t="n">
-        <v>3504</v>
+        <v>2115</v>
       </c>
       <c r="D6" t="n">
-        <v>1275</v>
+        <v>988</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>628</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>2328</v>
+        <v>807</v>
       </c>
       <c r="D7" t="n">
-        <v>696</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>265</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1308</v>
+        <v>408</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>577</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6287</v>
+        <v>781</v>
       </c>
       <c r="C2" t="n">
-        <v>16380</v>
+        <v>2898</v>
       </c>
       <c r="D2" t="n">
-        <v>38403</v>
+        <v>11489</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3803</v>
+        <v>1224</v>
       </c>
       <c r="C3" t="n">
-        <v>7751</v>
+        <v>5020</v>
       </c>
       <c r="D3" t="n">
-        <v>20529</v>
+        <v>15087</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2545</v>
+        <v>1367</v>
       </c>
       <c r="C4" t="n">
-        <v>6453</v>
+        <v>5770</v>
       </c>
       <c r="D4" t="n">
-        <v>9253</v>
+        <v>9422</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1829</v>
+        <v>690</v>
       </c>
       <c r="C5" t="n">
-        <v>5332</v>
+        <v>5783</v>
       </c>
       <c r="D5" t="n">
-        <v>3657</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1299</v>
+        <v>267</v>
       </c>
       <c r="C6" t="n">
-        <v>3972</v>
+        <v>2863</v>
       </c>
       <c r="D6" t="n">
-        <v>1479</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>759</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>2776</v>
+        <v>841</v>
       </c>
       <c r="D7" t="n">
-        <v>768</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>357</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1707</v>
+        <v>459</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>143</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>843</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>382</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>215</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5880</v>
+        <v>592</v>
       </c>
       <c r="C2" t="n">
-        <v>11269</v>
+        <v>3648</v>
       </c>
       <c r="D2" t="n">
-        <v>31707</v>
+        <v>13899</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4566</v>
+        <v>863</v>
       </c>
       <c r="C3" t="n">
-        <v>11939</v>
+        <v>3416</v>
       </c>
       <c r="D3" t="n">
-        <v>21564</v>
+        <v>13569</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1689</v>
+        <v>1155</v>
       </c>
       <c r="C4" t="n">
-        <v>8649</v>
+        <v>5294</v>
       </c>
       <c r="D4" t="n">
-        <v>8568</v>
+        <v>10168</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1200</v>
+        <v>884</v>
       </c>
       <c r="C5" t="n">
-        <v>3892</v>
+        <v>5711</v>
       </c>
       <c r="D5" t="n">
-        <v>2432</v>
+        <v>4304</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>701</v>
+        <v>407</v>
       </c>
       <c r="C6" t="n">
-        <v>2720</v>
+        <v>4318</v>
       </c>
       <c r="D6" t="n">
-        <v>752</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>329</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>1672</v>
+        <v>1788</v>
       </c>
       <c r="D7" t="n">
-        <v>470</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>826</v>
+        <v>628</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>374</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3642</v>
+        <v>336</v>
       </c>
       <c r="C2" t="n">
-        <v>5277</v>
+        <v>3105</v>
       </c>
       <c r="D2" t="n">
-        <v>22657</v>
+        <v>9989</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4449</v>
+        <v>662</v>
       </c>
       <c r="C3" t="n">
-        <v>10557</v>
+        <v>3153</v>
       </c>
       <c r="D3" t="n">
-        <v>21908</v>
+        <v>12943</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2416</v>
+        <v>970</v>
       </c>
       <c r="C4" t="n">
-        <v>10317</v>
+        <v>4416</v>
       </c>
       <c r="D4" t="n">
-        <v>10261</v>
+        <v>10478</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1310</v>
+        <v>946</v>
       </c>
       <c r="C5" t="n">
-        <v>5915</v>
+        <v>5682</v>
       </c>
       <c r="D5" t="n">
-        <v>3170</v>
+        <v>5043</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>828</v>
+        <v>511</v>
       </c>
       <c r="C6" t="n">
-        <v>3253</v>
+        <v>5015</v>
       </c>
       <c r="D6" t="n">
-        <v>926</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>2096</v>
+        <v>2703</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1076</v>
+        <v>950</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3287</v>
+        <v>618</v>
       </c>
       <c r="C2" t="n">
-        <v>3840</v>
+        <v>9542</v>
       </c>
       <c r="D2" t="n">
-        <v>21913</v>
+        <v>19899</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3460</v>
+        <v>439</v>
       </c>
       <c r="C3" t="n">
-        <v>7220</v>
+        <v>2739</v>
       </c>
       <c r="D3" t="n">
-        <v>20537</v>
+        <v>11627</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2830</v>
+        <v>738</v>
       </c>
       <c r="C4" t="n">
-        <v>10217</v>
+        <v>3723</v>
       </c>
       <c r="D4" t="n">
-        <v>11849</v>
+        <v>10585</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1568</v>
+        <v>881</v>
       </c>
       <c r="C5" t="n">
-        <v>7820</v>
+        <v>4956</v>
       </c>
       <c r="D5" t="n">
-        <v>4162</v>
+        <v>5776</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>943</v>
+        <v>635</v>
       </c>
       <c r="C6" t="n">
-        <v>4429</v>
+        <v>5321</v>
       </c>
       <c r="D6" t="n">
-        <v>1236</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>449</v>
+        <v>258</v>
       </c>
       <c r="C7" t="n">
-        <v>2603</v>
+        <v>3721</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1485</v>
+        <v>1697</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>519</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>662</v>
+        <v>637</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1984</v>
+        <v>405</v>
       </c>
       <c r="C2" t="n">
-        <v>1862</v>
+        <v>4809</v>
       </c>
       <c r="D2" t="n">
-        <v>15323</v>
+        <v>14327</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3300</v>
+        <v>657</v>
       </c>
       <c r="C3" t="n">
-        <v>5903</v>
+        <v>4954</v>
       </c>
       <c r="D3" t="n">
-        <v>20220</v>
+        <v>13048</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3098</v>
+        <v>1174</v>
       </c>
       <c r="C4" t="n">
-        <v>10035</v>
+        <v>5263</v>
       </c>
       <c r="D4" t="n">
-        <v>12848</v>
+        <v>11086</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1641</v>
+        <v>660</v>
       </c>
       <c r="C5" t="n">
-        <v>9570</v>
+        <v>7374</v>
       </c>
       <c r="D5" t="n">
-        <v>4430</v>
+        <v>5357</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>789</v>
+        <v>238</v>
       </c>
       <c r="C6" t="n">
-        <v>5178</v>
+        <v>5054</v>
       </c>
       <c r="D6" t="n">
-        <v>1216</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>2727</v>
+        <v>1663</v>
       </c>
       <c r="D7" t="n">
-        <v>569</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1085</v>
+        <v>624</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3073</v>
+        <v>262</v>
       </c>
       <c r="C2" t="n">
-        <v>9798</v>
+        <v>2720</v>
       </c>
       <c r="D2" t="n">
-        <v>14062</v>
+        <v>10056</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2378</v>
+        <v>462</v>
       </c>
       <c r="C3" t="n">
-        <v>3676</v>
+        <v>4292</v>
       </c>
       <c r="D3" t="n">
-        <v>18266</v>
+        <v>12411</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2784</v>
+        <v>779</v>
       </c>
       <c r="C4" t="n">
-        <v>8018</v>
+        <v>4799</v>
       </c>
       <c r="D4" t="n">
-        <v>13589</v>
+        <v>10633</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1970</v>
+        <v>629</v>
       </c>
       <c r="C5" t="n">
-        <v>9663</v>
+        <v>5638</v>
       </c>
       <c r="D5" t="n">
-        <v>5507</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1009</v>
+        <v>239</v>
       </c>
       <c r="C6" t="n">
-        <v>6954</v>
+        <v>5038</v>
       </c>
       <c r="D6" t="n">
-        <v>1644</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>295</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>3689</v>
+        <v>2261</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1685</v>
+        <v>686</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>547</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>137</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2178</v>
+        <v>323</v>
       </c>
       <c r="C2" t="n">
-        <v>4809</v>
+        <v>8063</v>
       </c>
       <c r="D2" t="n">
-        <v>11322</v>
+        <v>14467</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2274</v>
+        <v>305</v>
       </c>
       <c r="C3" t="n">
-        <v>5452</v>
+        <v>2994</v>
       </c>
       <c r="D3" t="n">
-        <v>16830</v>
+        <v>11140</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2461</v>
+        <v>551</v>
       </c>
       <c r="C4" t="n">
-        <v>6373</v>
+        <v>4412</v>
       </c>
       <c r="D4" t="n">
-        <v>13890</v>
+        <v>10651</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2099</v>
+        <v>636</v>
       </c>
       <c r="C5" t="n">
-        <v>9264</v>
+        <v>5115</v>
       </c>
       <c r="D5" t="n">
-        <v>6298</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1175</v>
+        <v>382</v>
       </c>
       <c r="C6" t="n">
-        <v>8030</v>
+        <v>5292</v>
       </c>
       <c r="D6" t="n">
-        <v>1953</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>265</v>
+        <v>124</v>
       </c>
       <c r="C7" t="n">
-        <v>4676</v>
+        <v>3697</v>
       </c>
       <c r="D7" t="n">
-        <v>712</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>2140</v>
+        <v>1448</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>602</v>
+        <v>461</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3583</v>
+        <v>391</v>
       </c>
       <c r="C2" t="n">
-        <v>10522</v>
+        <v>8419</v>
       </c>
       <c r="D2" t="n">
-        <v>14729</v>
+        <v>12181</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1888</v>
+        <v>261</v>
       </c>
       <c r="C3" t="n">
-        <v>4689</v>
+        <v>4841</v>
       </c>
       <c r="D3" t="n">
-        <v>15253</v>
+        <v>10968</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2084</v>
+        <v>379</v>
       </c>
       <c r="C4" t="n">
-        <v>5807</v>
+        <v>3571</v>
       </c>
       <c r="D4" t="n">
-        <v>13729</v>
+        <v>10309</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2028</v>
+        <v>547</v>
       </c>
       <c r="C5" t="n">
-        <v>7933</v>
+        <v>4650</v>
       </c>
       <c r="D5" t="n">
-        <v>7126</v>
+        <v>6847</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1374</v>
+        <v>458</v>
       </c>
       <c r="C6" t="n">
-        <v>8504</v>
+        <v>5149</v>
       </c>
       <c r="D6" t="n">
-        <v>2470</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>479</v>
+        <v>212</v>
       </c>
       <c r="C7" t="n">
-        <v>5857</v>
+        <v>4461</v>
       </c>
       <c r="D7" t="n">
-        <v>850</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>2984</v>
+        <v>2483</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>1089</v>
+        <v>896</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5311</v>
+        <v>2650</v>
       </c>
       <c r="C2" t="n">
-        <v>6522</v>
+        <v>3653</v>
       </c>
       <c r="D2" t="n">
-        <v>7655</v>
+        <v>14157</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2617</v>
+        <v>669</v>
       </c>
       <c r="C2" t="n">
-        <v>6144</v>
+        <v>22639</v>
       </c>
       <c r="D2" t="n">
-        <v>10958</v>
+        <v>15691</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2559</v>
+        <v>259</v>
       </c>
       <c r="C3" t="n">
-        <v>6424</v>
+        <v>5691</v>
       </c>
       <c r="D3" t="n">
-        <v>16522</v>
+        <v>10395</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2938</v>
+        <v>284</v>
       </c>
       <c r="C4" t="n">
-        <v>8513</v>
+        <v>4106</v>
       </c>
       <c r="D4" t="n">
-        <v>13835</v>
+        <v>10103</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1288</v>
+        <v>442</v>
       </c>
       <c r="C5" t="n">
-        <v>11860</v>
+        <v>4056</v>
       </c>
       <c r="D5" t="n">
-        <v>6365</v>
+        <v>7104</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="C6" t="n">
-        <v>7239</v>
+        <v>4828</v>
       </c>
       <c r="D6" t="n">
-        <v>1910</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>283</v>
       </c>
       <c r="C7" t="n">
-        <v>2924</v>
+        <v>4762</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>1067</v>
+        <v>3315</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>1524</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>537</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>201</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6970</v>
+        <v>3196</v>
       </c>
       <c r="C2" t="n">
-        <v>6991</v>
+        <v>6079</v>
       </c>
       <c r="D2" t="n">
-        <v>12361</v>
+        <v>22501</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2257</v>
+        <v>878</v>
       </c>
       <c r="C3" t="n">
-        <v>3287</v>
+        <v>1442</v>
       </c>
       <c r="D3" t="n">
-        <v>1925</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4543</v>
+        <v>1739</v>
       </c>
       <c r="C2" t="n">
-        <v>6003</v>
+        <v>3644</v>
       </c>
       <c r="D2" t="n">
-        <v>19202</v>
+        <v>18410</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3786</v>
+        <v>1724</v>
       </c>
       <c r="C3" t="n">
-        <v>4698</v>
+        <v>3645</v>
       </c>
       <c r="D3" t="n">
-        <v>3536</v>
+        <v>5864</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1014</v>
+        <v>433</v>
       </c>
       <c r="C4" t="n">
-        <v>1968</v>
+        <v>947</v>
       </c>
       <c r="D4" t="n">
-        <v>1569</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4861</v>
+        <v>2165</v>
       </c>
       <c r="C2" t="n">
-        <v>6461</v>
+        <v>3693</v>
       </c>
       <c r="D2" t="n">
-        <v>20174</v>
+        <v>19453</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3425</v>
+        <v>1427</v>
       </c>
       <c r="C3" t="n">
-        <v>4682</v>
+        <v>3131</v>
       </c>
       <c r="D3" t="n">
-        <v>5787</v>
+        <v>7540</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2029</v>
+        <v>959</v>
       </c>
       <c r="C4" t="n">
-        <v>3473</v>
+        <v>2559</v>
       </c>
       <c r="D4" t="n">
-        <v>1898</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>477</v>
+        <v>234</v>
       </c>
       <c r="C5" t="n">
-        <v>1169</v>
+        <v>635</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5011</v>
+        <v>2486</v>
       </c>
       <c r="C2" t="n">
-        <v>6328</v>
+        <v>5600</v>
       </c>
       <c r="D2" t="n">
-        <v>21658</v>
+        <v>25564</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3374</v>
+        <v>1479</v>
       </c>
       <c r="C3" t="n">
-        <v>4872</v>
+        <v>2974</v>
       </c>
       <c r="D3" t="n">
-        <v>7566</v>
+        <v>8986</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2322</v>
+        <v>1036</v>
       </c>
       <c r="C4" t="n">
-        <v>4017</v>
+        <v>2840</v>
       </c>
       <c r="D4" t="n">
-        <v>2531</v>
+        <v>3378</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1024</v>
+        <v>514</v>
       </c>
       <c r="C5" t="n">
-        <v>2361</v>
+        <v>1711</v>
       </c>
       <c r="D5" t="n">
-        <v>1297</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>271</v>
+        <v>157</v>
       </c>
       <c r="C6" t="n">
-        <v>740</v>
+        <v>461</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>292</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5830</v>
+        <v>2292</v>
       </c>
       <c r="C2" t="n">
-        <v>8300</v>
+        <v>7076</v>
       </c>
       <c r="D2" t="n">
-        <v>29911</v>
+        <v>35394</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3071</v>
+        <v>1609</v>
       </c>
       <c r="C3" t="n">
-        <v>4600</v>
+        <v>3797</v>
       </c>
       <c r="D3" t="n">
-        <v>8632</v>
+        <v>10991</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1756</v>
+        <v>1072</v>
       </c>
       <c r="C4" t="n">
-        <v>3646</v>
+        <v>2855</v>
       </c>
       <c r="D4" t="n">
-        <v>2921</v>
+        <v>4352</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>871</v>
+        <v>676</v>
       </c>
       <c r="C5" t="n">
-        <v>2365</v>
+        <v>2282</v>
       </c>
       <c r="D5" t="n">
-        <v>1202</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="C6" t="n">
-        <v>1044</v>
+        <v>1103</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>905</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C7" t="n">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4402</v>
+        <v>2110</v>
       </c>
       <c r="C2" t="n">
-        <v>9583</v>
+        <v>10945</v>
       </c>
       <c r="D2" t="n">
-        <v>34232</v>
+        <v>32870</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3701</v>
+        <v>1583</v>
       </c>
       <c r="C3" t="n">
-        <v>5839</v>
+        <v>4753</v>
       </c>
       <c r="D3" t="n">
-        <v>11727</v>
+        <v>13926</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2119</v>
+        <v>1142</v>
       </c>
       <c r="C4" t="n">
-        <v>4156</v>
+        <v>3292</v>
       </c>
       <c r="D4" t="n">
-        <v>4038</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1165</v>
+        <v>757</v>
       </c>
       <c r="C5" t="n">
-        <v>3078</v>
+        <v>2526</v>
       </c>
       <c r="D5" t="n">
-        <v>1512</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>550</v>
+        <v>429</v>
       </c>
       <c r="C6" t="n">
-        <v>1791</v>
+        <v>1657</v>
       </c>
       <c r="D6" t="n">
-        <v>831</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>291</v>
+        <v>335</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5191</v>
+        <v>1917</v>
       </c>
       <c r="C2" t="n">
-        <v>9084</v>
+        <v>6567</v>
       </c>
       <c r="D2" t="n">
-        <v>34549</v>
+        <v>25377</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3333</v>
+        <v>2092</v>
       </c>
       <c r="C3" t="n">
-        <v>6821</v>
+        <v>7794</v>
       </c>
       <c r="D3" t="n">
-        <v>14483</v>
+        <v>15746</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2483</v>
+        <v>699</v>
       </c>
       <c r="C4" t="n">
-        <v>5022</v>
+        <v>4542</v>
       </c>
       <c r="D4" t="n">
-        <v>5391</v>
+        <v>5132</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1447</v>
+        <v>396</v>
       </c>
       <c r="C5" t="n">
-        <v>3574</v>
+        <v>1623</v>
       </c>
       <c r="D5" t="n">
-        <v>1912</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>774</v>
+        <v>164</v>
       </c>
       <c r="C6" t="n">
-        <v>2462</v>
+        <v>716</v>
       </c>
       <c r="D6" t="n">
-        <v>943</v>
+        <v>649</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>324</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>1297</v>
+        <v>328</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>521</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
